--- a/reports/빅딜/history/2026-06-10/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-06-10/빅딜_league_mgf_report.xlsx
@@ -80,7 +80,7 @@
     <t>Scania 20</t>
   </si>
   <si>
-    <t>368</t>
+    <t>367</t>
   </si>
   <si>
     <t>4위</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>1660조 5620억 2663만</t>
+    <t>1670조 8734억 4025만</t>
   </si>
   <si>
     <t>함께 성장해가실 토벌전점수 160억이상 용사님들 모집중입니다 신청 후 귓말주세요(단톡방 자유 희망시 귓) (철새 금지)</t>
@@ -113,7 +113,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>360</t>
+    <t>362</t>
   </si>
   <si>
     <t>10위</t>
@@ -140,10 +140,10 @@
     <t>Scania 7</t>
   </si>
   <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>1752조 6414억 2262만</t>
+    <t>358</t>
+  </si>
+  <si>
+    <t>1762조 8728억 5383만</t>
   </si>
   <si>
     <t>신규 가입 문의 토벌 200억 이상\n 길드컨텐츠 필참\n 풀접 환영 \n 귓말 '망치물어, 일단해바, 미궁왕' -&amp;gt; 가입 절차 및 상담</t>
@@ -167,7 +167,7 @@
     <t>21위</t>
   </si>
   <si>
-    <t>1871조 8591억 2668만</t>
+    <t>1879조 591억 6271만</t>
   </si>
   <si>
     <t>투력 3조 이상 / 길드 콘텐츠 필수참여 / 공지방(필수참여) 단톡방(자유참여)</t>
@@ -185,10 +185,10 @@
     <t>Scania 22</t>
   </si>
   <si>
-    <t>367</t>
-  </si>
-  <si>
-    <t>8위</t>
+    <t>352</t>
+  </si>
+  <si>
+    <t>7위</t>
   </si>
   <si>
     <t>Lv.7</t>
@@ -197,7 +197,7 @@
     <t>27명</t>
   </si>
   <si>
-    <t>1660조 9836억 5261만</t>
+    <t>1813조 3619억 813만</t>
   </si>
   <si>
     <t>모기가앙해따 많관부^.^</t>
@@ -317,6 +317,18 @@
     <t>6</t>
   </si>
   <si>
+    <t>워터붐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%8C%ED%84%B0%EB%B6%90</t>
+  </si>
+  <si>
+    <t>66조 1277억 2446만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>바넷사</t>
   </si>
   <si>
@@ -332,18 +344,6 @@
     <t>64조 3819억 6909만</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>워터붐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%8C%ED%84%B0%EB%B6%90</t>
-  </si>
-  <si>
-    <t>64조 1846억 1946만</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -422,7 +422,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>39조 9166억 5734만</t>
+    <t>41조 1113억 8492만</t>
   </si>
   <si>
     <t>14</t>
@@ -434,7 +434,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%EB%B3%B4%EB%A6%AC%EC%95%84%EB%B9%A0</t>
   </si>
   <si>
-    <t>39조 7670억 964만</t>
+    <t>40조 5812억 4774만</t>
   </si>
   <si>
     <t>15</t>
@@ -485,7 +485,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%A8%ED%95%A8%ED%99%8D</t>
   </si>
   <si>
-    <t>27조 922억 4036만</t>
+    <t>29조 2265억 8844만</t>
   </si>
   <si>
     <t>19</t>
@@ -602,6 +602,30 @@
     <t>28</t>
   </si>
   <si>
+    <t>킹종빈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EC%A2%85%EB%B9%88</t>
+  </si>
+  <si>
+    <t>15조 1933억 1819만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>루몽몽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%AA%BD%EB%AA%BD</t>
+  </si>
+  <si>
+    <t>14조 4176억 1578만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>찍먹영재</t>
   </si>
   <si>
@@ -611,30 +635,6 @@
     <t>14조 3716억 5477만</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>킹종빈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EC%A2%85%EB%B9%88</t>
-  </si>
-  <si>
-    <t>14조 3179억 196만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>루몽몽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EB%AA%BD%EB%AA%BD</t>
-  </si>
-  <si>
-    <t>14조 1791억 1409만</t>
-  </si>
-  <si>
     <t>킹몬</t>
   </si>
   <si>
@@ -959,7 +959,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%95%EC%B0%A9%EC%86%8C%EB%85%84%EB%8B%A8</t>
   </si>
   <si>
-    <t>50조 4374억 6750만</t>
+    <t>50조 5534억 2967만</t>
+  </si>
+  <si>
+    <t>짱구는묙말라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EA%B5%AC%EB%8A%94%EB%AC%99%EB%A7%90%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>50조 3129억 920만</t>
   </si>
   <si>
     <t>스토퍼</t>
@@ -971,15 +980,6 @@
     <t>47조 7045억 6695만</t>
   </si>
   <si>
-    <t>짱구는묙말라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EA%B5%AC%EB%8A%94%EB%AC%99%EB%A7%90%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>46조 7026억 8765만</t>
-  </si>
-  <si>
     <t>킴하린</t>
   </si>
   <si>
@@ -1100,7 +1100,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B6%81%ED%83%84</t>
   </si>
   <si>
-    <t>19조 3456억 3582만</t>
+    <t>19조 3882억 8813만</t>
   </si>
   <si>
     <t>쉬다</t>
@@ -1166,7 +1166,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A5%AC%ED%8E%98</t>
   </si>
   <si>
-    <t>724조 4931억 7650만</t>
+    <t>724조 5008억 5691만</t>
   </si>
   <si>
     <t>케넨</t>
@@ -1175,7 +1175,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BC%80%EB%84%A8</t>
   </si>
   <si>
-    <t>157조 4016억 5525만</t>
+    <t>161조 7542억 9383만</t>
   </si>
   <si>
     <t>캡숑짱짱</t>
@@ -1283,7 +1283,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%96%87%EB%B9%9B</t>
   </si>
   <si>
-    <t>25조 7070억 5709만</t>
+    <t>26조 2594억 3610만</t>
+  </si>
+  <si>
+    <t>하이이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>23조 780억 5769만</t>
   </si>
   <si>
     <t>소망</t>
@@ -1292,16 +1301,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%A7%9D</t>
   </si>
   <si>
-    <t>21조 5795억 9517만</t>
-  </si>
-  <si>
-    <t>하이이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%9D%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>21조 522억 7677만</t>
+    <t>21조 5994억 8831만</t>
   </si>
   <si>
     <t>의밍</t>
@@ -1385,7 +1385,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>1589조 4455억 304만</t>
+    <t>1741조 5325억 8292만</t>
   </si>
   <si>
     <t>노루상</t>
@@ -1412,7 +1412,7 @@
     <t>https://mgf.gg/contents/character.php?n=Sausage</t>
   </si>
   <si>
-    <t>8조 769억 8850만</t>
+    <t>8조 1717억 7046만</t>
   </si>
   <si>
     <t>애니메이트</t>
@@ -1424,6 +1424,15 @@
     <t>7조 63억 6699만</t>
   </si>
   <si>
+    <t>인생별거없다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EC%83%9D%EB%B3%84%EA%B1%B0%EC%97%86%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>3조 5489억 680만</t>
+  </si>
+  <si>
     <t>로툐</t>
   </si>
   <si>
@@ -1436,15 +1445,6 @@
     <t>3조 5368억 6603만</t>
   </si>
   <si>
-    <t>인생별거없다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EC%83%9D%EB%B3%84%EA%B1%B0%EC%97%86%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>3조 4767억 7770만</t>
-  </si>
-  <si>
     <t>SEXXXXXXXXXY</t>
   </si>
   <si>
@@ -1454,6 +1454,15 @@
     <t>3조 850억 1251만</t>
   </si>
   <si>
+    <t>심구슬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EA%B5%AC%EC%8A%AC</t>
+  </si>
+  <si>
+    <t>3조 438억 8261만</t>
+  </si>
+  <si>
     <t>폼프로</t>
   </si>
   <si>
@@ -1461,15 +1470,6 @@
   </si>
   <si>
     <t>2조 9599억 9412만</t>
-  </si>
-  <si>
-    <t>심구슬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EA%B5%AC%EC%8A%AC</t>
-  </si>
-  <si>
-    <t>2조 9229억 9391만</t>
   </si>
   <si>
     <t>소소동자</t>
@@ -2403,13 +2403,13 @@
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2420,25 +2420,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>104</v>
@@ -2470,7 +2470,7 @@
         <v>108</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>109</v>
@@ -2502,7 +2502,7 @@
         <v>113</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>114</v>
@@ -2566,7 +2566,7 @@
         <v>77</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>122</v>
@@ -2630,7 +2630,7 @@
         <v>130</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>131</v>
@@ -2694,7 +2694,7 @@
         <v>113</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>139</v>
@@ -2790,7 +2790,7 @@
         <v>113</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>152</v>
@@ -2819,7 +2819,7 @@
         <v>70</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>147</v>
@@ -2854,7 +2854,7 @@
         <v>113</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>160</v>
@@ -2918,7 +2918,7 @@
         <v>108</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>168</v>
@@ -2950,7 +2950,7 @@
         <v>172</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>173</v>
@@ -3107,7 +3107,7 @@
         <v>70</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>172</v>
+        <v>108</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>147</v>
@@ -3139,7 +3139,7 @@
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>147</v>
@@ -3171,7 +3171,7 @@
         <v>70</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>147</v>
@@ -3464,7 +3464,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>219</v>
@@ -3514,7 +3514,7 @@
         <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>224</v>
@@ -3642,7 +3642,7 @@
         <v>172</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>236</v>
@@ -3706,7 +3706,7 @@
         <v>108</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>243</v>
@@ -3770,7 +3770,7 @@
         <v>172</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>249</v>
@@ -3834,7 +3834,7 @@
         <v>92</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>255</v>
@@ -3927,7 +3927,7 @@
         <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>147</v>
@@ -4122,7 +4122,7 @@
         <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>282</v>
@@ -4430,7 +4430,7 @@
         <v>172</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>304</v>
@@ -4476,7 +4476,7 @@
         <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>308</v>
@@ -4494,7 +4494,7 @@
         <v>108</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>310</v>
@@ -4523,7 +4523,7 @@
         <v>70</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>87</v>
@@ -4555,10 +4555,10 @@
         <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>316</v>
@@ -4782,7 +4782,7 @@
         <v>108</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>337</v>
@@ -4846,7 +4846,7 @@
         <v>77</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>343</v>
@@ -4942,7 +4942,7 @@
         <v>108</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>352</v>
@@ -5102,7 +5102,7 @@
         <v>77</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>366</v>
@@ -5134,7 +5134,7 @@
         <v>108</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>369</v>
@@ -5195,7 +5195,7 @@
         <v>70</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>375</v>
@@ -5488,7 +5488,7 @@
         <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>395</v>
@@ -5634,7 +5634,7 @@
         <v>130</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>409</v>
@@ -5666,7 +5666,7 @@
         <v>92</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>412</v>
@@ -5698,7 +5698,7 @@
         <v>92</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>415</v>
@@ -5759,10 +5759,10 @@
         <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>421</v>
@@ -5791,10 +5791,10 @@
         <v>70</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>424</v>
@@ -5858,7 +5858,7 @@
         <v>92</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>430</v>
@@ -5890,7 +5890,7 @@
         <v>77</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>433</v>
@@ -6102,7 +6102,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6286,7 +6286,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>239</v>
@@ -6318,13 +6318,13 @@
         <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>172</v>
+        <v>113</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6335,25 +6335,25 @@
         <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>471</v>
